--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_11.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03235545040565323</v>
+        <v>0.02812644252114115</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008471071234002286</v>
+        <v>0.008464239976449508</v>
       </c>
       <c r="C2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>46426978</v>
+        <v>4045994</v>
       </c>
       <c r="L2" t="n">
-        <v>23684177</v>
+        <v>1634885</v>
       </c>
       <c r="M2" t="n">
-        <v>5263512</v>
+        <v>278042</v>
       </c>
       <c r="N2" t="n">
-        <v>195151</v>
+        <v>4641</v>
       </c>
       <c r="O2" t="n">
-        <v>3255839</v>
+        <v>174823</v>
       </c>
       <c r="P2" t="n">
-        <v>1179646</v>
+        <v>29208</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999841451644897</v>
+        <v>0.9999825954437256</v>
       </c>
       <c r="R2" t="n">
-        <v>0.809994101524353</v>
+        <v>0.7111683487892151</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6604310870170593</v>
+        <v>0.5328753590583801</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5778790712356567</v>
+        <v>0.3971132338047028</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2208097577095032</v>
+        <v>0.045680932700634</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6278737783432007</v>
+        <v>0.4257008731365204</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7693686485290527</v>
+        <v>0.6238093376159668</v>
       </c>
       <c r="X2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52478774</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32815898</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8820770</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>649524</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5058909</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9557238221168518</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118883609771729</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583142161369324</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617491245269775</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020285606384277</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008640958185208417</v>
+        <v>0.00737344004137261</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002031164118261611</v>
+        <v>0.002029011818888065</v>
       </c>
       <c r="C3" t="n">
-        <v>467</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>46426978</v>
+        <v>4045994</v>
       </c>
       <c r="E3" t="n">
-        <v>8085617</v>
+        <v>859938</v>
       </c>
       <c r="F3" t="n">
-        <v>251298</v>
+        <v>31766</v>
       </c>
       <c r="G3" t="n">
-        <v>18961</v>
+        <v>2583</v>
       </c>
       <c r="H3" t="n">
-        <v>21521</v>
+        <v>3590</v>
       </c>
       <c r="I3" t="n">
-        <v>731</v>
+        <v>71</v>
       </c>
       <c r="J3" t="n">
-        <v>109890256</v>
+        <v>10016512</v>
       </c>
       <c r="K3" t="n">
-        <v>113454131</v>
+        <v>9742417</v>
       </c>
       <c r="L3" t="n">
-        <v>130901038</v>
+        <v>11563926</v>
       </c>
       <c r="M3" t="n">
-        <v>165015125</v>
+        <v>14963728</v>
       </c>
       <c r="N3" t="n">
-        <v>177479185</v>
+        <v>16142685</v>
       </c>
       <c r="O3" t="n">
-        <v>171608379</v>
+        <v>15581249</v>
       </c>
       <c r="P3" t="n">
-        <v>176668236</v>
+        <v>16118054</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8471214771270752</v>
+        <v>0.8183717727661133</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6565834283828735</v>
+        <v>0.4905859529972076</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5114943981170654</v>
+        <v>0.2946121692657471</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1986130177974701</v>
+        <v>0.05158959701657295</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5801193118095398</v>
+        <v>0.3411160409450531</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5542029738426208</v>
+        <v>0.1506094932556152</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52478774</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2158656</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>92853</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74703</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>109891353</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>121913622</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>139907703</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167403857</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>177835829</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>172988579</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>176875999</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575445055961609</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097371101379395</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571794629096985</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610466837882996</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013869762420654</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.071522012081083</v>
+        <v>0.06385510160817309</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03202834854031932</v>
+        <v>0.03200610849614379</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9975443</v>
+        <v>1465108</v>
       </c>
       <c r="E4" t="n">
-        <v>23684177</v>
+        <v>1634885</v>
       </c>
       <c r="F4" t="n">
-        <v>2021390</v>
+        <v>181222</v>
       </c>
       <c r="G4" t="n">
-        <v>104966</v>
+        <v>15506</v>
       </c>
       <c r="H4" t="n">
-        <v>265464</v>
+        <v>34334</v>
       </c>
       <c r="I4" t="n">
-        <v>20388</v>
+        <v>1456</v>
       </c>
       <c r="J4" t="n">
-        <v>1097</v>
+        <v>110</v>
       </c>
       <c r="K4" t="n">
-        <v>10890696</v>
+        <v>1643227</v>
       </c>
       <c r="L4" t="n">
-        <v>12177516</v>
+        <v>1433159</v>
       </c>
       <c r="M4" t="n">
-        <v>3844816</v>
+        <v>422116</v>
       </c>
       <c r="N4" t="n">
-        <v>688646</v>
+        <v>96955</v>
       </c>
       <c r="O4" t="n">
-        <v>1929660</v>
+        <v>235848</v>
       </c>
       <c r="P4" t="n">
-        <v>353619</v>
+        <v>17614</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999920725822449</v>
+        <v>0.9999912977218628</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8281419277191162</v>
+        <v>0.7610132098197937</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6585016846656799</v>
+        <v>0.5108569860458374</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5426640510559082</v>
+        <v>0.3382683098316193</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2091240435838699</v>
+        <v>0.04845580458641052</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6030526161193848</v>
+        <v>0.3787433207035065</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6442966461181641</v>
+        <v>0.2426377087831497</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2270831</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32815898</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>911085</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60790</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12494</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2431205</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3170851</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1456084</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332002</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549460</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566332697868347</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9108114838600159</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577464818954468</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613976955413818</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901707649230957</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>657219</v>
+        <v>132107</v>
       </c>
       <c r="E5" t="n">
-        <v>3245406</v>
+        <v>423589</v>
       </c>
       <c r="F5" t="n">
-        <v>5263512</v>
+        <v>278042</v>
       </c>
       <c r="G5" t="n">
-        <v>222706</v>
+        <v>25243</v>
       </c>
       <c r="H5" t="n">
-        <v>822718</v>
+        <v>79384</v>
       </c>
       <c r="I5" t="n">
-        <v>78790</v>
+        <v>5371</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8378595</v>
+        <v>897962</v>
       </c>
       <c r="L5" t="n">
-        <v>12387669</v>
+        <v>1697630</v>
       </c>
       <c r="M5" t="n">
-        <v>5026947</v>
+        <v>665714</v>
       </c>
       <c r="N5" t="n">
-        <v>787418</v>
+        <v>85319</v>
       </c>
       <c r="O5" t="n">
-        <v>2356522</v>
+        <v>337680</v>
       </c>
       <c r="P5" t="n">
-        <v>948899</v>
+        <v>164724</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999938607215881</v>
+        <v>0.9999932646751404</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8924406766891479</v>
+        <v>0.8443814516067505</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8628795146942139</v>
+        <v>0.8082752227783203</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9504786729812622</v>
+        <v>0.9333829283714294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9917607307434082</v>
+        <v>0.9888378381729126</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9760749340057373</v>
+        <v>0.9648780226707458</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9927294850349426</v>
+        <v>0.9888339042663574</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88331</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>943632</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8820770</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109731</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321032</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2326799</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3255948</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1469689</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333045</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553452</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734413027763367</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641262292861938</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836686253547668</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962877631187439</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993843674659729</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998367965221405</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>177926</v>
+        <v>24469</v>
       </c>
       <c r="E6" t="n">
-        <v>238256</v>
+        <v>27866</v>
       </c>
       <c r="F6" t="n">
-        <v>246515</v>
+        <v>24034</v>
       </c>
       <c r="G6" t="n">
-        <v>195151</v>
+        <v>4641</v>
       </c>
       <c r="H6" t="n">
-        <v>113418</v>
+        <v>8384</v>
       </c>
       <c r="I6" t="n">
-        <v>11139</v>
+        <v>544</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71548</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58765</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120515</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>649524</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76925</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>161</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>74540</v>
+        <v>19793</v>
       </c>
       <c r="E7" t="n">
-        <v>550060</v>
+        <v>108302</v>
       </c>
       <c r="F7" t="n">
-        <v>1195097</v>
+        <v>156802</v>
       </c>
       <c r="G7" t="n">
-        <v>294093</v>
+        <v>42596</v>
       </c>
       <c r="H7" t="n">
-        <v>3255839</v>
+        <v>174823</v>
       </c>
       <c r="I7" t="n">
-        <v>242571</v>
+        <v>10172</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8907</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>327984</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83851</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5058909</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>5568</v>
+        <v>1750</v>
       </c>
       <c r="E8" t="n">
-        <v>58177</v>
+        <v>13464</v>
       </c>
       <c r="F8" t="n">
-        <v>130516</v>
+        <v>28292</v>
       </c>
       <c r="G8" t="n">
-        <v>47920</v>
+        <v>11027</v>
       </c>
       <c r="H8" t="n">
-        <v>706539</v>
+        <v>110156</v>
       </c>
       <c r="I8" t="n">
-        <v>1179646</v>
+        <v>29208</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
